--- a/artfynd/A 26989-2025 artfynd.xlsx
+++ b/artfynd/A 26989-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115838276</v>
+        <v>115768684</v>
       </c>
       <c r="B2" t="n">
-        <v>56598</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100038</v>
+        <v>100090</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,16 +710,8 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hyltan, Finnsjöområdet, Råda, Vg</t>
@@ -761,12 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hörde minst två nötkråkor kommunicera med varandra</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,12 +788,7 @@
         <v>115838228</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,6 +895,117 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>117343654</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hyltan våtmark, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>330368</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6392208</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Råda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Robin Åberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Robin Åberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26989-2025 artfynd.xlsx
+++ b/artfynd/A 26989-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115768684</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115838228</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,8 +1021,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117343654</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>